--- a/www/download/COUNTRY.JPN.WIOD16.xlsx
+++ b/www/download/COUNTRY.JPN.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Japão</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>107.739232579634</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>121.420670096829</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>125.169447913313</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>115.72962298913</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>3035430.4036899</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>4631975.61740371</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>103.811303598629</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>117.646088969639</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>103.094908874959</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>93.4544503073286</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>87.6063315891266</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.784</t>
+          <t>79.7365501555935</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>79.7486323800894</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>97.4573381706102</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>105.66323170126</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>65.252</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>64.76</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>63.747</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>63.536</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>63.676</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>63.916</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>64.198</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>64.438</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>64.21</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>63.274</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>62.989</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>62.858</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>62.498</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>62.041</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>61.234</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>53.892</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>53.794</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>53.186</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>53.136</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>53.316</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>53.791</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>54.574</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>55.012</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>55.06</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>54.399</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>54.389</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>54.455</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>54.275</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>53.993</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>53.31</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>119243.178</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>117456.865</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>114587.472</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>114337.246</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>114700.225</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>114245.012</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>115079.656</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>115249.215</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>113633.208</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>108862.472</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>109633.813</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>108990.363</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>109076.429</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>108181.505</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>106612.053</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>99508.392</t>
+          <t>199498030036.284</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>98380.036</t>
+          <t>189372301563.967</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96354.936</t>
+          <t>181909112336.32</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>96365.669</t>
+          <t>188462668201.806</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>96723.76</t>
+          <t>195845757089.566</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>96839.829</t>
+          <t>195025137370.367</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>98632.02</t>
+          <t>199176122454.615</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>99149.193</t>
+          <t>193107685889.201</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>98093.174</t>
+          <t>199670945213.005</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>94098.707</t>
+          <t>177617158331.847</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>95242.37</t>
+          <t>184190367419.304</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>95002.359</t>
+          <t>204238227035.992</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>95308.515</t>
+          <t>202754012004.448</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>94708.474</t>
+          <t>190877223520.441</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>93356.966</t>
+          <t>187794268987.903</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>77081965805.8465</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>73166260233.7656</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>69636804715.4756</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>71775833056.1982</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>74073612660.8939</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>73723395637.7857</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>72166445323.0391</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>63337574217.7434</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>61617407386.345</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>59110835796.35</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>57493645267.3246</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>62774548209.2356</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>60611719008.2791</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>56332525960.778</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>55128667483.2789</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1595717.90619162</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1738156.69288917</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1777647.10431599</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1731993.95687018</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1618906.89898116</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1572925.7829968</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1602623.97655525</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1466258.40044456</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1294158.311243</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1284818.8917754</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1169829.01870534</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1173210.48618001</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1151415.89691714</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1317550.81636993</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1390369.57345413</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>505845.941175948</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>487804.437689952</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>475250.286230143</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>516797.798378507</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>571036.031645039</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>610328.028212833</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>652096.532066978</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>734941.662728097</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>782311.653243908</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>668076.528844512</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>752591.844308879</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>802221.649918326</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>786984.62388359</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>772947.00464581</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>762216.677100338</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1620994.54334283</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1524256.46300703</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1472973.34689901</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1660783.85637604</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1908059.53050491</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2040056.75235416</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2201058.66667794</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2409422.97539756</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2704071.81762024</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2189002.69853509</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2514906.11991461</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2961438.57960092</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2864508.85306208</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2694033.18635129</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2662798.66473898</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.290942588187761</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.344609329664747</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.383678311557949</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.342592136110057</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.305778900346032</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.313556278766498</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.366729641199491</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.565408752475151</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.591971780230051</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.591902839475845</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.656572125252409</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.513389776336503</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.572443684759734</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.681239610503914</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.693437730892301</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1185138.49433602</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1096647.11427096</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1075989.48354226</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1184499.71263843</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1255024.98469275</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1231816.21756874</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1178385.43123057</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1162996.69932027</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1323611.91537455</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1505242.51245923</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1647884.24854522</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1774831.98019559</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1754750.47410304</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1371820.5073622</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1248641.36416907</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>107.739232579634</t>
+          <t>1430.30071094091</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>121.420670096829</t>
+          <t>1360.12961470769</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>125.169447913313</t>
+          <t>1309.31203481184</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>115.72962298913</t>
+          <t>1350.78431733027</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3035430.4036899</t>
+          <t>1389.32160244729</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4631975.61740371</t>
+          <t>1370.56091151884</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>103.811303598629</t>
+          <t>1322.35054737578</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>117.646088969639</t>
+          <t>1151.335432115</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>103.094908874959</t>
+          <t>1119.09660350745</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>93.4544503073286</t>
+          <t>1086.61724195468</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>87.6063315891266</t>
+          <t>1057.08588338092</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>79.7365501555935</t>
+          <t>1152.77992125432</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>79.7486323800894</t>
+          <t>1116.75108765342</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>97.4573381706102</t>
+          <t>1043.3319313697</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>105.66323170126</t>
+          <t>1034.1074395539</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>95406784678.704</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.125</t>
+          <t>84481385709.301</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>84481935743.8728</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>91037432434.2106</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.323</t>
+          <t>99694310151.0241</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>94633648757.7924</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>87987184218.3511</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>77192826283.3547</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>71609534841.4566</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>61947617053.9896</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.839</t>
+          <t>65981710507.9159</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3.102</t>
+          <t>66921292572.7272</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.078</t>
+          <t>63138178709.9849</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>56484531440.9055</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.335</t>
+          <t>55524110895.3558</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.816</t>
+          <t>94818748284.1122</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>85590309083.8377</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.283</t>
+          <t>85483563967.6839</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.481</t>
+          <t>89312100060.2301</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.629</t>
+          <t>97274799848.1803</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.623</t>
+          <t>91632526526.2352</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>84704219467.5612</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2.499</t>
+          <t>74176384276.1654</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.825</t>
+          <t>66609768367.4273</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.954</t>
+          <t>58067771456.384</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>61090386756.3958</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3.446</t>
+          <t>62368325915.6955</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>3.419</t>
+          <t>58689240608.6286</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>53317329705.345</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.588</t>
+          <t>53233016527.253</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12.929</t>
+          <t>588036394.591812</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.916</t>
+          <t>-1108923374.53672</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.931</t>
+          <t>-1001628223.81111</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13.133</t>
+          <t>1725332373.98053</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14.175</t>
+          <t>2419510302.84387</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.014</t>
+          <t>3001122231.55718</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>13.222</t>
+          <t>3282964750.78987</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>12.973</t>
+          <t>3016442007.18925</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>14.465</t>
+          <t>4999766474.02932</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>3879845597.60555</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>17.531</t>
+          <t>4891323751.52008</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>19.107</t>
+          <t>4552966657.03164</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>19.114</t>
+          <t>4448938101.35624</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>15.486</t>
+          <t>3167201735.56049</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>13.976</t>
+          <t>2291094368.1028</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.691</t>
+          <t>1846.43610166886</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7.607</t>
+          <t>1828.84296948928</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7.256</t>
+          <t>1811.66666563095</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.845</t>
+          <t>1813.55240202841</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.566</t>
+          <t>1814.1468342706</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8.633</t>
+          <t>1800.30889075751</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.378</t>
+          <t>1807.29568915486</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8.489</t>
+          <t>1802.31056246758</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9.691</t>
+          <t>1781.57021213517</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9.355</t>
+          <t>1729.78907289107</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10.317</t>
+          <t>1751.13900840664</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>11.271</t>
+          <t>1744.60534719229</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11.351</t>
+          <t>1756.02819522918</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>9.378</t>
+          <t>1754.09096992228</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>8.669</t>
+          <t>1751.19655593701</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.638</t>
+          <t>1827.41659597536</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.046</t>
+          <t>1813.7247380944</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.886</t>
+          <t>1797.52110855186</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1799.560464536</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.554</t>
+          <t>1801.30847191198</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1787.41208324298</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>1792.58267080039</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>4.311</t>
+          <t>1788.53651418931</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.796</t>
+          <t>1769.72298215954</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.929</t>
+          <t>1720.48426939895</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5.411</t>
+          <t>1740.52724063108</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>5.838</t>
+          <t>1733.91093531739</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>5.872</t>
+          <t>1745.29021657904</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>1743.70174088165</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>1741.06334543731</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>514755.885383471</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>435043.796871403</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>448737.41223068</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>511777.3725861</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>615418.912609876</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>655648.017034086</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>704741.873642375</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>773816.535009029</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>861051.278612774</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>640035.978022185</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>835356.191170724</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>894167.16715149</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>874812.429494343</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>795706.144001027</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>817514.175625425</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>15816827715.3862</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15673163476.4497</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>16362301599.2193</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>17198544449.2678</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>19393577572.9463</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20399114075.3621</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22627188643.9269</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>23504767807.2996</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>23574799115.2589</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>17759224741.6973</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>21024478193.5108</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>23256418528.5631</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>22252821208.9575</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>23733569735.59</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>25953677187.4899</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>416389.773809825</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>381989.202066191</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>370197.395407604</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>411069.127841153</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>490288.927139523</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>556258.816926937</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>607987.400284405</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>656601.036029451</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>782668.768445338</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>574199.182540807</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>712369.641505279</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>881845.349987746</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>918369.791408372</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>862402.90127541</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>889352.675789581</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>119243.178</t>
+          <t>96025954866.4952</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>117456.865</t>
+          <t>91661044987.6706</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>114587.472</t>
+          <t>88161943769.9553</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>114337.246</t>
+          <t>92913561442.6665</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>114700.225</t>
+          <t>101820577093.446</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>114245.012</t>
+          <t>102500572970.131</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>115079.656</t>
+          <t>99510156680.7397</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>115249.215</t>
+          <t>89233836108.6122</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>113633.208</t>
+          <t>88436267331.8491</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>108862.472</t>
+          <t>73297640259.2065</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>109633.813</t>
+          <t>76369970090.2467</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>108990.363</t>
+          <t>89166714338.4081</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>109076.429</t>
+          <t>89003170612.2195</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>108181.505</t>
+          <t>85779950666.0956</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>106612.053</t>
+          <t>87409928879.0702</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>99508.392</t>
+          <t>98366.1115736465</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>98380.036</t>
+          <t>53054.5948052114</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96354.936</t>
+          <t>78540.0168230759</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>96365.669</t>
+          <t>100708.244744947</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>96723.76</t>
+          <t>125129.985470352</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>96839.829</t>
+          <t>99389.2001071495</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>98632.02</t>
+          <t>96754.4733579702</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>99149.193</t>
+          <t>117215.498979578</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>98093.174</t>
+          <t>78382.5101674357</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>94098.707</t>
+          <t>65836.7954813783</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>95242.37</t>
+          <t>122986.549665445</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>95002.359</t>
+          <t>12321.8171637439</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>95308.515</t>
+          <t>-43557.3619140283</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>94708.474</t>
+          <t>-66696.7572743831</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>93356.966</t>
+          <t>-71838.5001641564</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>199434.221</t>
+          <t>-80209127151.109</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>189782.347</t>
+          <t>-75987881511.221</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>182298.076</t>
+          <t>-71799642170.736</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>188773.688</t>
+          <t>-75715016993.3987</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>196162.802</t>
+          <t>-82426999520.4998</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>195320.756</t>
+          <t>-82101458894.7692</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>198845.132</t>
+          <t>-76882968036.8128</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>193192.315</t>
+          <t>-65729068301.3126</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>199806.412</t>
+          <t>-64861468216.5903</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>177338.015</t>
+          <t>-55538415517.5093</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>184190.677</t>
+          <t>-55345491896.7359</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>204612.514</t>
+          <t>-65910295809.845</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>203104.568</t>
+          <t>-66750349403.262</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>191019.567</t>
+          <t>-62046380930.5056</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>188109.056</t>
+          <t>-61456251691.5802</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2101343.16159578</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1788650.59646181</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1696556.74159477</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1835669.85230868</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>2002980.48207818</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>1975149.08987265</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.197</t>
+          <t>1862584.05775429</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1855055.00306071</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>2024231.06734807</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>2037513.77624551</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.515</t>
+          <t>2293851.19172707</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.966</t>
+          <t>2429631.33829554</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.869</t>
+          <t>2449792.57611224</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.696</t>
+          <t>2018454.91790564</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>1874777.74484558</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>62255.156</t>
+          <t>0.0492686534936036</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>60604.4</t>
+          <t>0.0448463928545294</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>58692.411</t>
+          <t>0.0441855484840278</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>58645.255</t>
+          <t>0.0406867823667132</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>58611.895</t>
+          <t>0.0472582704677065</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>58346.077</t>
+          <t>0.0482120374528402</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>59008.904</t>
+          <t>0.043081523394985</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>58903.267</t>
+          <t>0.0500378912762133</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>57766.553</t>
+          <t>0.044781668636049</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>54208.181</t>
+          <t>0.0286764142776705</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>55119.421</t>
+          <t>0.0344936066041907</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>55325.925</t>
+          <t>0.0322949110628721</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>55703.891</t>
+          <t>0.0365180054512008</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>54764.722</t>
+          <t>0.0412401818406613</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>53755.444</t>
+          <t>0.0430211042936547</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>2467901.05404877</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>2124892.09688782</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>2012027.95893069</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>2189765.2133933</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>2323326.13621388</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2325025.67422874</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>2283967.95758722</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>2230458.83236105</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>2532930.44617965</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>2647996.04275366</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>2839127.01333372</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>3101639.5901877</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>3078394.0533017</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>2532564.95184708</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>2335376.08391695</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>77077.223</t>
+          <t>2815746.98017517</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>73233.861</t>
+          <t>2415279.67896613</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>69695.882</t>
+          <t>2282877.34837872</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>71824.384</t>
+          <t>2480875.94726225</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>74127.439</t>
+          <t>2629016.94674353</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>73773.413</t>
+          <t>2622651.06991303</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>72118.043</t>
+          <t>2562197.19764021</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>63347.16</t>
+          <t>2498606.06263854</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>61627.266</t>
+          <t>2825108.00660218</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>59067.759</t>
+          <t>2954291.44972516</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>57496.765</t>
+          <t>3158809.2828684</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>62840.317</t>
+          <t>3446481.09334626</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>60662.938</t>
+          <t>3418845.63587703</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>56356.386</t>
+          <t>2809894.0431069</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>55180.497</t>
+          <t>2588002.54392296</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>12929335.5367143</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>11916248.1822585</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>11930682.2949141</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>13133073.3797242</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>14175074.1519047</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>14014397.2369244</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>13222088.9201837</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>12972963.6033805</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>14464963.8271289</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>59.31</t>
+          <t>16379891.3059061</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>17530536.5673627</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>19107114.3572554</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>19113785.2474752</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>15485864.1604196</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>69.18</t>
+          <t>13975539.7359382</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>2657690.65933312</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>2581393.75852712</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2534035.9685786</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>2576048.79614849</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>2581464.83334509</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>2636021.5794875</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2747169.37625104</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>2732797.46923889</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>2722924.19971649</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>2595992.15486235</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2568532.26484767</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>2572981.1930315</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>2601815.54751729</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>2605182.93053314</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>2577524.82812196</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2324161.73332826</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2266316.30516248</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2228241.8129017</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2267518.14926057</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2278198.58539989</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2335500.31988763</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2446802.63278462</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2439022.15946194</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2440906.51913833</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2327463.6633351</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2308588.04282968</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2318607.91988719</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2347935.25399895</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2352982.06356535</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2331223.60956321</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1822149.44679694</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1631047.8616046</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1603153.22453172</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1718842.21104534</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1924914.47286326</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1907478.86203431</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1748013.16437603</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1812136.44163649</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1971377.13231347</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1974959.0613706</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2252575.68046021</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2391894.53903128</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2452747.78796342</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2010460.36129768</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1849884.51670899</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99508392440</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>98380036127</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>96354936371</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>96365669024</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>96723760485</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>96839829232</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>98632019923</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>99149193041</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>98093173730</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>94098707348</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>95242370129</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>95002359474</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>95308514777</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>94708474005</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>93356965570</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>119243177528.611</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>117456864760.35</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>114587472329.208</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>114337245779.594</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>114700224883.941</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>114245012397.374</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>115079655742.997</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>115249214671.485</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>113633208138.101</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>108862472009.081</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>109633812578.106</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>108990363467.158</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>109076429086.599</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>108181505268.47</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>106612052983.583</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>62255156367.364</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>60604400453.8606</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>58692411432.7743</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>58645254546.1036</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>58611894521.6298</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>58346076600.9756</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>59008903619.6537</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>58903266550.6008</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>57766552735.9515</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>54208181050.2002</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>55119420650.4738</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>55325924568.4869</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>55703891334.6835</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>54764721875.9967</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>53755443692.3521</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>65252322.7551</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>64760027.9653</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>63747497.4753</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>63536206.7754</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>63676059.1939</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>63916437.3277</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>64197683.9437</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>64437719.7542</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>64209601.8889</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>63274319.8792</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>62988851.8943</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>62858109.5183</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>62497588.1091</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>62041289.9363</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>61233873.6916</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>53892139.7551</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>53793593.9653</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>53185797.4753</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>53136412.7754</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>53316390.1939</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>53790674.3277</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>54574367.9437</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>55012268.7542</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>55059953.8889</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>54398948.8792</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>54388811.8943</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>54454928.5183</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>54275048.1091</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>53992908.9363</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>53310386.6916</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>119243177528.611</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>117456864760.35</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>114587472329.208</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>114337245779.594</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>114700224883.941</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>114245012397.374</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>115079655742.997</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>115249214671.485</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>113633208138.101</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>108862472009.081</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>109633812578.106</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>108990363467.158</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>109076429086.599</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>108181505268.47</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>106612052983.583</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99508392440</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>98380036127</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96354936371</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>96365669024</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>96723760485</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>96839829232</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>98632019923</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>99149193041</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>98093173730</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>94098707348</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>95242370129</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>95002359474</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>95308514777</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>94708474005</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>93356965570</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8691188.71794</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7607273.101566</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7255717.057897</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7844807.361578</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8566025.20592</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>8632723.076474</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8377589.479347</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>8489260.46098099</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>9691283.5756</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>9354837.54048</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>10317384.1940403</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>11271277.3727482</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>11351477.6356733</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>9378218.96326445</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>8668735.69674184</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4637896.423278</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4046327.518474</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3886030.554791</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4199718.158394</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4553931.41858948</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>4530129.95094718</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>4310210.37749763</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>4310742.49993999</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4796485.14136</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4929250.54416</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>5411384.96780317</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>5838375.60511275</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>5871593.42879351</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>4820354.38468313</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>4437887.09869627</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>12405127.7534928</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12911112.704854</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>13422804.7596975</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>13842429.9426662</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>14075888.6945473</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>14142664.4139113</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>14191408.1613297</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>14025861.3774479</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>13672344.8313649</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>13880174.0024465</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>14254658.9139682</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>14262094.0516948</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>14310644.6178311</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>14152104.0985708</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>13628469.5712574</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
